--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיתריי – שיהא בי את האומץ</v>
+        <v>נטע ברזילי – אוקסיטוצין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%aa%d7%a8%d7%99%d7%99-%d7%a9%d7%99%d7%94%d7%90-%d7%91%d7%99-%d7%90%d7%aa-%d7%94%d7%90%d7%95%d7%9e%d7%a5/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%90%d7%95%d7%a7%d7%a1%d7%99%d7%98%d7%95%d7%a6%d7%99%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שיהא בי את האומץ” של מיתריי (מאיה ביתנר) הוא שיר שממוקם בין תפילה אישית לבין טקס קולקטיבי. זה לא רק שיר במובן הפופולרי אלא חוויה כמעט מדיטטיבית־שבטית, שמבקשת לפרק פחדים ולהזמין חופש. ליבת  השיר נמצאת במשפט החוזר: "שיהא בי את</v>
+        <v>"אוקסיטוצין" של נטע ברזילי (מתוך האלבום "סרנדה") מציג צד שקט, עדין ואינטימי יחסית למה שמזוהה איתה בדרך כלל. במקום אנרגיה מתפרצת והפקה אלקטרונית, יש כאן בלדה רכה עם נגיעות של בוסה נובה ועיבוד אקוסטי מינימליסטי – בחירה שמשרתת  את התוכן</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיתריי – שיהא בי את האומץ</v>
+        <v>נטע ברזילי – אוקסיטוצין</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – אוקסיטוצין</v>
+        <v>רותם שפי – רילוקיישן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%90%d7%95%d7%a7%d7%a1%d7%99%d7%98%d7%95%d7%a6%d7%99%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%a9%d7%a4%d7%99-%d7%a8%d7%99%d7%9c%d7%95%d7%a7%d7%99%d7%99%d7%a9%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"אוקסיטוצין" של נטע ברזילי (מתוך האלבום "סרנדה") מציג צד שקט, עדין ואינטימי יחסית למה שמזוהה איתה בדרך כלל. במקום אנרגיה מתפרצת והפקה אלקטרונית, יש כאן בלדה רכה עם נגיעות של בוסה נובה ועיבוד אקוסטי מינימליסטי – בחירה שמשרתת  את התוכן</v>
+        <v>"רילוקיישן" של רותם שפי הוא טקסט שנשען על קלילות לכאורה,  אבל מתחתיה מסתתרת אמירה חדה על חיים בתוך מציאות לא יציבה. הוא משלב ראפ עם R&amp;B גרובי והפקה אלקטרונית, שמייצרת תחושת זרימה כמעט “כיפית”, בניגוד מעניין לתוכן הכאוטי. בפתיחה יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – אוקסיטוצין</v>
+        <v>רותם שפי – רילוקיישן</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם שפי – רילוקיישן</v>
+        <v>רוני בר הדס – אמא מלכה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%aa%d7%9d-%d7%a9%d7%a4%d7%99-%d7%a8%d7%99%d7%9c%d7%95%d7%a7%d7%99%d7%99%d7%a9%d7%9f/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%91%d7%a8-%d7%94%d7%93%d7%a1-%d7%90%d7%9e%d7%90-%d7%9e%d7%9c%d7%9b%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-29</v>
+        <v>2026-04-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"רילוקיישן" של רותם שפי הוא טקסט שנשען על קלילות לכאורה,  אבל מתחתיה מסתתרת אמירה חדה על חיים בתוך מציאות לא יציבה. הוא משלב ראפ עם R&amp;B גרובי והפקה אלקטרונית, שמייצרת תחושת זרימה כמעט “כיפית”, בניגוד מעניין לתוכן הכאוטי. בפתיחה יש</v>
+        <v>“אמא מלכה” של רוני בר הדס הוא פופ עכשווי שמצליח להיות גם קליט ושובב  וגם רגשי וכנה מתחת לפני השטח. יש כאן עטיפה מתקתקה, כמעט “מרקידה”, שבתוכה יושב טקסט חשוף על מועקה, בדידות ודימוי עצמי. “יש לי אלף ואחת סיבות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם שפי – רילוקיישן</v>
+        <v>רוני בר הדס – אמא מלכה</v>
       </c>
     </row>
   </sheetData>
